--- a/engine/scem_study/SCEM_Valuation_Model_07092026_public.xlsx
+++ b/engine/scem_study/SCEM_Valuation_Model_07092026_public.xlsx
@@ -4406,7 +4406,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>straight-line</t>
+          <t>BOOK charge only — not the terminal life</t>
         </is>
       </c>
     </row>
@@ -4452,6 +4452,21 @@
       <c r="C24" s="5" t="inlineStr">
         <is>
           <t>EGP mn</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Disclosed useful life, machinery (note 3/2)</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>years; 5% on machinery, 69.5% of note 4 gross cost</t>
         </is>
       </c>
     </row>
@@ -5189,11 +5204,11 @@
         </is>
       </c>
       <c r="B89" s="23" t="n">
-        <v>958.8325110000001</v>
+        <v>1241.175</v>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Replacement capital over the note 3/2 life — the SAME charge the terminal makes</t>
+          <t>Replacement capital over the note 3/2 MACHINERY life — the SAME charge the terminal makes</t>
         </is>
       </c>
     </row>
@@ -7915,7 +7930,7 @@
         </is>
       </c>
       <c r="B45" s="34">
-        <f>1/Assumptions!$B$21</f>
+        <f>Assumptions!$B$25</f>
         <v/>
       </c>
       <c r="C45" s="36">

--- a/engine/scem_study/SCEM_Valuation_Model_07092026_public.xlsx
+++ b/engine/scem_study/SCEM_Valuation_Model_07092026_public.xlsx
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="B12" s="32">
-        <f>C12-Assumptions!$B$66</f>
+        <f>C12-Assumptions!$B$66-Assumptions!$B$75</f>
         <v/>
       </c>
       <c r="C12" s="32">
@@ -1341,35 +1341,35 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>The FY2024 column is the DISCLOSED triple — total assets EGP 6,385.92mn less total liabilities EGP</t>
+          <t>The FY2024 column is the DISCLOSED triple, taken from the audited statements for that year: total assets</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>1,610.86mn closes to equity of EGP 4,775.06mn exactly. Equity then ROLLS FORWARD: prior equity plus</t>
+          <t>EGP 5,695.61mn less total liabilities EGP 1,959.81mn closes to equity of EGP 3,735.80mn exactly.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>profit less dividends. Row 13 carries the REPORTED FY2025 equity beside the rolled figure: the two do</t>
+          <t>FY2023 rolls BACK through the year's profit AND the EGP 1,277.47mn paid in under the capital increase, to the</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>not agree, and the gap implies a FY2025 distribution that no retrievable source reports. Disclosed, not</t>
+          <t>filed EGP -614.03mn. Rolling FY2024 forward by FY2025 profit gives EGP 6,020.34mn against a reported EGP</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>plugged. Row 11 is the residual liability block, not an independently sourced line.</t>
+          <t>6,020.34mn — they agree to the pound. Row 11 is the residual liability block, not an independently sourced line.</t>
         </is>
       </c>
     </row>
@@ -2553,19 +2553,19 @@
         <v>0.2595969690413578</v>
       </c>
       <c r="B6" s="18" t="n">
-        <v>100.3949039578356</v>
+        <v>98.69050917203239</v>
       </c>
       <c r="C6" s="18" t="n">
-        <v>104.3156499111916</v>
+        <v>101.8679131291328</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>108.8079510287171</v>
+        <v>105.497941259736</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>114.003878181809</v>
+        <v>109.6851827142112</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>120.0795886170832</v>
+        <v>114.5691393869592</v>
       </c>
     </row>
     <row r="7">
@@ -2573,19 +2573,19 @@
         <v>0.2745969690413578</v>
       </c>
       <c r="B7" s="18" t="n">
-        <v>99.16754112323778</v>
+        <v>97.49505860858825</v>
       </c>
       <c r="C7" s="18" t="n">
-        <v>103.0148769083448</v>
+        <v>100.6129703767378</v>
       </c>
       <c r="D7" s="18" t="n">
-        <v>107.4230663326401</v>
+        <v>104.1750316002814</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>112.5217074358182</v>
+        <v>108.2838731524603</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>118.4836591806312</v>
+        <v>113.0763849610594</v>
       </c>
     </row>
     <row r="8">
@@ -2593,19 +2593,19 @@
         <v>0.2895969690413578</v>
       </c>
       <c r="B8" s="18" t="n">
-        <v>97.97094810507103</v>
+        <v>96.32955012837782</v>
       </c>
       <c r="C8" s="18" t="n">
-        <v>101.7467778180994</v>
+        <v>99.38951280237987</v>
       </c>
       <c r="D8" s="18" t="n">
-        <v>106.0730372190444</v>
+        <v>102.8853700289691</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>111.076915655642</v>
+        <v>106.9178451976036</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>116.9280593569136</v>
+        <v>111.6212840180454</v>
       </c>
     </row>
     <row r="9">
@@ -2613,19 +2613,19 @@
         <v>0.3045969690413578</v>
       </c>
       <c r="B9" s="18" t="n">
-        <v>96.80410052545189</v>
+        <v>95.19298730155951</v>
       </c>
       <c r="C9" s="18" t="n">
-        <v>100.5102639716144</v>
+        <v>98.19649187431013</v>
       </c>
       <c r="D9" s="18" t="n">
-        <v>104.7567013559794</v>
+        <v>101.6278484901775</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>109.6682553084179</v>
+        <v>105.5859221331662</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>115.4114419857919</v>
+        <v>110.2025797561083</v>
       </c>
     </row>
     <row r="10">
@@ -2633,19 +2633,19 @@
         <v>0.3195969690413578</v>
       </c>
       <c r="B10" s="18" t="n">
-        <v>95.66601685634413</v>
+        <v>94.08441537150684</v>
       </c>
       <c r="C10" s="18" t="n">
-        <v>99.30429225659127</v>
+        <v>97.0329029275219</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>103.4729450693056</v>
+        <v>100.4014053010241</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>108.2945311061131</v>
+        <v>104.2869765060833</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>113.9325163463356</v>
+        <v>108.8190680084981</v>
       </c>
     </row>
     <row r="12">
@@ -2690,19 +2690,19 @@
         </is>
       </c>
       <c r="B14" s="18" t="n">
-        <v>111.1768007620267</v>
+        <v>105.8700254231585</v>
       </c>
       <c r="C14" s="18" t="n">
-        <v>114.0524300594702</v>
+        <v>108.7456547206019</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>116.9280593569136</v>
+        <v>111.6212840180454</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>119.8036886543571</v>
+        <v>114.4969133154889</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>122.6793179518006</v>
+        <v>117.3725426129323</v>
       </c>
     </row>
     <row r="16">
@@ -2761,19 +2761,19 @@
         </is>
       </c>
       <c r="B22" s="18" t="n">
-        <v>144.3637450871468</v>
+        <v>136.8257338962387</v>
       </c>
       <c r="C22" s="18" t="n">
-        <v>128.8993522294487</v>
+        <v>122.6262163486371</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>126.4596017523283</v>
+        <v>120.3844455455019</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>116.9280593569136</v>
+        <v>111.6212840180454</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>103.3293889329463</v>
+        <v>99.10136066798457</v>
       </c>
     </row>
     <row r="24">
@@ -2818,19 +2818,19 @@
         </is>
       </c>
       <c r="B26" s="18" t="n">
-        <v>104.4772836031017</v>
+        <v>99.69517959957598</v>
       </c>
       <c r="C26" s="18" t="n">
-        <v>110.7026714800077</v>
+        <v>105.6582318088107</v>
       </c>
       <c r="D26" s="18" t="n">
-        <v>116.9280593569136</v>
+        <v>111.6212840180454</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>123.1534472338196</v>
+        <v>117.5843362272801</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>129.3788351107256</v>
+        <v>123.5473884365149</v>
       </c>
     </row>
     <row r="28">
@@ -5020,21 +5020,21 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FY2024 total assets</t>
+          <t>FY2024 total assets  (audited, as filed)</t>
         </is>
       </c>
       <c r="B69" s="21" t="n">
-        <v>6385.92</v>
+        <v>5695.60821</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FY2024 total liabilities</t>
+          <t>FY2024 total liabilities  (audited, as filed)</t>
         </is>
       </c>
       <c r="B70" s="21" t="n">
-        <v>1610.86</v>
+        <v>1959.808479</v>
       </c>
     </row>
     <row r="72">
@@ -5080,6 +5080,16 @@
         <is>
           <t>mn</t>
         </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Paid under capital increase during FY2024  (audited, as filed)</t>
+        </is>
+      </c>
+      <c r="B75" s="21" t="n">
+        <v>1277.4661</v>
       </c>
     </row>
     <row r="79">
@@ -5184,7 +5194,7 @@
         </is>
       </c>
       <c r="B87" s="18" t="n">
-        <v>21.59798678191003</v>
+        <v>22.36203179396409</v>
       </c>
     </row>
     <row r="88">
@@ -5194,7 +5204,7 @@
         </is>
       </c>
       <c r="B88" s="18" t="n">
-        <v>92.91616012464766</v>
+        <v>90.36890796199091</v>
       </c>
     </row>
     <row r="89">
@@ -7733,7 +7743,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Terminal NOPAT</t>
+          <t>Terminal NOPAT — the first perpetuity year, a diagnostic beside the return above</t>
         </is>
       </c>
       <c r="B28" s="31">
@@ -7918,6 +7928,10 @@
           <t>Normalised risk-free rate</t>
         </is>
       </c>
+      <c r="B44" s="31">
+        <f>F11</f>
+        <v/>
+      </c>
       <c r="C44" s="36">
         <f>C42+C43</f>
         <v/>
@@ -7945,7 +7959,7 @@
         </is>
       </c>
       <c r="B46" s="31">
-        <f>DCF!F8*(1+Assumptions!$B$55)</f>
+        <f>DCF!F8</f>
         <v/>
       </c>
       <c r="C46" s="39">
@@ -7975,7 +7989,7 @@
         </is>
       </c>
       <c r="B48" s="31">
-        <f>B28+B46-B25-B47</f>
+        <f>B44+B46-B25-B47</f>
         <v/>
       </c>
       <c r="C48" s="36">
